--- a/Samples/Budget.xlsx
+++ b/Samples/Budget.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Suppliers" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,19 +29,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Helvetica Neue"/>
+      <color rgb="0026222F"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Helvetica Neue"/>
       <b val="1"/>
       <color rgb="0026222F"/>
-      <sz val="14"/>
+      <sz val="16"/>
     </font>
     <font>
+      <name val="Helvetica Neue"/>
+      <color rgb="007A7185"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Helvetica Neue"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="12"/>
     </font>
     <font>
+      <name val="Helvetica Neue"/>
       <b val="1"/>
+      <color rgb="0026222F"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -52,8 +74,13 @@
         <fgColor rgb="00F86F5B"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDF3EC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -62,23 +89,53 @@
       <diagonal/>
     </border>
     <border>
+      <bottom style="thin">
+        <color rgb="00EADFD6"/>
+      </bottom>
+    </border>
+    <border>
       <top style="medium">
         <color rgb="0026222F"/>
       </top>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -444,200 +501,547 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Harbor Street Bakery — Q4 budget</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+          <t>Harbor Street Bakery — second half budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>July to December 2026 · all three shops</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>October</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>November</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>December</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="19" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Flour &amp; grain</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B5" s="6" t="n">
+        <v>4100</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>4150</v>
+      </c>
+      <c r="D5" s="6" t="n">
         <v>4200</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="E5" s="6" t="n">
+        <v>4200</v>
+      </c>
+      <c r="F5" s="6" t="n">
         <v>4300</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="G5" s="6" t="n">
         <v>4900</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>13400</v>
+      <c r="H5" s="7" t="n">
+        <v>25850</v>
+      </c>
+    </row>
+    <row r="6" ht="19" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Butter &amp; dairy</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>3050</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>3100</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>3100</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>3600</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="7" ht="19" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Eggs</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>900</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>920</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>940</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>950</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>980</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>5840</v>
+      </c>
+    </row>
+    <row r="8" ht="19" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Coffee beans</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>1750</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>1780</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>1750</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>2100</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>10980</v>
+      </c>
+    </row>
+    <row r="9" ht="19" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Fruit &amp; nuts</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>1050</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="10" ht="19" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Wages</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>21200</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>21300</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>21500</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>21500</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>24800</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>131300</v>
+      </c>
+    </row>
+    <row r="11" ht="19" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>6200</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>6200</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>6200</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>6200</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>6200</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>37200</v>
+      </c>
+    </row>
+    <row r="12" ht="19" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>1350</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>1400</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>1450</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>1900</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="13" ht="19" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>610</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>615</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>620</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>640</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>900</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>3985</v>
+      </c>
+    </row>
+    <row r="14" ht="19" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>250</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>480</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>120</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>300</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="15" ht="19" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="n">
+        <v>40350</v>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>40580</v>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>41315</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>40920</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>41290</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>47250</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>251705</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Suppliers</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Who we order from, and when</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Supplier</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Supplies</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Order day</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Terms</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Butter &amp; dairy</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>3100</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>3150</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>3600</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>9850</v>
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Millbrook Flour</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Flour, rye, spelt</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>30 days</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Green Valley Dairy</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Butter, milk, cream</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Mon &amp; Thu</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>14 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Harbor Roasters</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Coffee beans</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>1800</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>1750</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>2100</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>5650</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Wages</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>21500</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>21500</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>24800</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>67800</v>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>30 days</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Rent</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>6200</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>6200</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>6200</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>18600</v>
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Orchard Lane</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Fruit, nuts</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>On delivery</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>1450</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>1600</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>1900</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>4950</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Packaging</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>620</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>900</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>2160</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>38870</v>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>39140</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>44400</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>122410</v>
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Paper &amp; Co</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Boxes, bags, cups</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>30 days</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Samples/Budget.xlsx
+++ b/Samples/Budget.xlsx
@@ -879,6 +879,10 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1045,6 +1049,10 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>